--- a/ai8-cert-challenge/evaluation/Ragas Evaluation Comparison.xlsx
+++ b/ai8-cert-challenge/evaluation/Ragas Evaluation Comparison.xlsx
@@ -101,20 +101,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEA9999"/>
+        <bgColor rgb="FFEA9999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB6D7A8"/>
         <bgColor rgb="FFB6D7A8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEA9999"/>
-        <bgColor rgb="FFEA9999"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9DAF8"/>
-        <bgColor rgb="FFC9DAF8"/>
+        <fgColor rgb="FF9FC5E8"/>
+        <bgColor rgb="FF9FC5E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -383,7 +383,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="4">
-        <v>0.131601731601731</v>
+        <v>0.142272727272727</v>
       </c>
     </row>
     <row r="4">
@@ -391,7 +391,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="4">
-        <v>0.769557782159768</v>
+        <v>0.766804365666283</v>
       </c>
     </row>
     <row r="5">
@@ -482,11 +482,11 @@
       </c>
       <c r="B18" s="6">
         <f t="shared" ref="B18:B21" si="1">B11-B3</f>
-        <v>0.005064935065</v>
+        <v>-0.005606060606</v>
       </c>
       <c r="C18" s="7">
-        <f t="shared" ref="C18:C21" si="2">B18*100</f>
-        <v>0.5064935065</v>
+        <f t="shared" ref="C18:C21" si="2">B18*100/B3</f>
+        <v>-3.940362087</v>
       </c>
     </row>
     <row r="19">
@@ -495,11 +495,11 @@
       </c>
       <c r="B19" s="6">
         <f t="shared" si="1"/>
-        <v>-0.001913179652</v>
+        <v>0.0008402368414</v>
       </c>
       <c r="C19" s="8">
         <f t="shared" si="2"/>
-        <v>-0.1913179652</v>
+        <v>0.109576429</v>
       </c>
     </row>
     <row r="20">
